--- a/Python/Strings Comparer/ExcelData/driver-app-string.xlsx
+++ b/Python/Strings Comparer/ExcelData/driver-app-string.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="951">
   <si>
     <t>Key</t>
   </si>
@@ -1647,6 +1647,1224 @@
   </si>
   <si>
     <t>View details with images</t>
+  </si>
+  <si>
+    <t>button_add_new_customization_sd</t>
+  </si>
+  <si>
+    <t>Add new customization</t>
+  </si>
+  <si>
+    <t>button_add_sd</t>
+  </si>
+  <si>
+    <t>Add {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>button_admin</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>button_arrived_at_pick_location_ss</t>
+  </si>
+  <si>
+    <t>Pick from location</t>
+  </si>
+  <si>
+    <t>button_arrived_at_pick_up</t>
+  </si>
+  <si>
+    <t>Arrived at pick up</t>
+  </si>
+  <si>
+    <t>button_cancel_order_qd</t>
+  </si>
+  <si>
+    <t>Cancel Order</t>
+  </si>
+  <si>
+    <t>button_chat</t>
+  </si>
+  <si>
+    <t>Chat</t>
+  </si>
+  <si>
+    <t>button_download</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t>button_drop_order</t>
+  </si>
+  <si>
+    <t>Drop order</t>
+  </si>
+  <si>
+    <t>button_dropoff_onsite_ss</t>
+  </si>
+  <si>
+    <t>Drop at my location after service</t>
+  </si>
+  <si>
+    <t>button_individual</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>button_lets_get_started</t>
+  </si>
+  <si>
+    <t>Let's get Started</t>
+  </si>
+  <si>
+    <t>button_on_site_service_ss</t>
+  </si>
+  <si>
+    <t>On-Site</t>
+  </si>
+  <si>
+    <t>button_online_service_ss</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>button_order_delivered</t>
+  </si>
+  <si>
+    <t>Service Complete</t>
+  </si>
+  <si>
+    <t>button_pickup_onsite_ss</t>
+  </si>
+  <si>
+    <t>Pick at my location</t>
+  </si>
+  <si>
+    <t>button_pickup_service_ss</t>
+  </si>
+  <si>
+    <t>At Home</t>
+  </si>
+  <si>
+    <t>button_schedule</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>button_select_business</t>
+  </si>
+  <si>
+    <t>button_service_complete</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>button_service_pause</t>
+  </si>
+  <si>
+    <t>button_service_start</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>button_start_assessment</t>
+  </si>
+  <si>
+    <t>button_swipe_to_pick_order</t>
+  </si>
+  <si>
+    <t>Pick Order</t>
+  </si>
+  <si>
+    <t>button_swipe_to_start_delivery</t>
+  </si>
+  <si>
+    <t>button_tap_when_you_arrived_at_stop</t>
+  </si>
+  <si>
+    <t>Arrived at stop - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>button_unavailable_this_day</t>
+  </si>
+  <si>
+    <t>Tap to unavailable This Day</t>
+  </si>
+  <si>
+    <t>button_update</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>button_view_cancellation_policy</t>
+  </si>
+  <si>
+    <t>View Cancellation Policy</t>
+  </si>
+  <si>
+    <t>button_view_cart_qd</t>
+  </si>
+  <si>
+    <t>View Cart</t>
+  </si>
+  <si>
+    <t>button_view_referral_policy</t>
+  </si>
+  <si>
+    <t>View Referral Policy</t>
+  </si>
+  <si>
+    <t>button_workflow_service_provider</t>
+  </si>
+  <si>
+    <t>Service Provider</t>
+  </si>
+  <si>
+    <t>button_workflow_taxi_delivery</t>
+  </si>
+  <si>
+    <t>Taxi Driver/Delivery Provider</t>
+  </si>
+  <si>
+    <t>description_accepted</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>description_additional_info</t>
+  </si>
+  <si>
+    <t>Additional info</t>
+  </si>
+  <si>
+    <t>description_allow_drop_at_home</t>
+  </si>
+  <si>
+    <t>Allow Drop At Home</t>
+  </si>
+  <si>
+    <t>description_allow_pickup_from_home</t>
+  </si>
+  <si>
+    <t>Allow Pickup From Home</t>
+  </si>
+  <si>
+    <t>description_applied_on</t>
+  </si>
+  <si>
+    <t>Applied On ({{_VALUE}})</t>
+  </si>
+  <si>
+    <t>description_are_you_sure_remove_item</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove?</t>
+  </si>
+  <si>
+    <t>description_athome_service_tag_ss</t>
+  </si>
+  <si>
+    <t>description_bank_pending</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>description_bank_processing</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>description_bank_verified</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>description_billing_details</t>
+  </si>
+  <si>
+    <t>BILLING DETAILS</t>
+  </si>
+  <si>
+    <t>description_billing_details_qd</t>
+  </si>
+  <si>
+    <t>description_complete_in_mins_ss</t>
+  </si>
+  <si>
+    <t>Complete in {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_courier</t>
+  </si>
+  <si>
+    <t>Courier</t>
+  </si>
+  <si>
+    <t>description_courier_group_tag</t>
+  </si>
+  <si>
+    <t>Courier Group</t>
+  </si>
+  <si>
+    <t>description_courier_modifier</t>
+  </si>
+  <si>
+    <t>Modifier</t>
+  </si>
+  <si>
+    <t>description_customer</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>description_customer_address</t>
+  </si>
+  <si>
+    <t>Customer Address</t>
+  </si>
+  <si>
+    <t>description_delete_address</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete this address?</t>
+  </si>
+  <si>
+    <t>description_delivery_in_min_qd</t>
+  </si>
+  <si>
+    <t>Delivery in {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_departure_time</t>
+  </si>
+  <si>
+    <t>Departure Time: {{_UNIT_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_dimension</t>
+  </si>
+  <si>
+    <t>Dimension - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_doc_expired</t>
+  </si>
+  <si>
+    <t>Expired</t>
+  </si>
+  <si>
+    <t>description_download_successfully</t>
+  </si>
+  <si>
+    <t>Download Successfully</t>
+  </si>
+  <si>
+    <t>description_driver</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>description_drop_off_items</t>
+  </si>
+  <si>
+    <t>Drop off items</t>
+  </si>
+  <si>
+    <t>description_dropoff_onsite_tag_ss</t>
+  </si>
+  <si>
+    <t>Delivery at my location</t>
+  </si>
+  <si>
+    <t>description_express_delivery</t>
+  </si>
+  <si>
+    <t>Express Delivery</t>
+  </si>
+  <si>
+    <t>description_fix_group_booking</t>
+  </si>
+  <si>
+    <t>Fix Group Booking</t>
+  </si>
+  <si>
+    <t>description_fix_group_ride_days</t>
+  </si>
+  <si>
+    <t>Fix Group Ride Days</t>
+  </si>
+  <si>
+    <t>description_friday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>description_hyperpay</t>
+  </si>
+  <si>
+    <t>Hyperpay</t>
+  </si>
+  <si>
+    <t>description_images</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>description_in_app_google</t>
+  </si>
+  <si>
+    <t>In App Navigation</t>
+  </si>
+  <si>
+    <t>description_includes_items_in_this_order</t>
+  </si>
+  <si>
+    <t>Include {{_QUANTITY}} items in this order</t>
+  </si>
+  <si>
+    <t>description_inter_city_courier</t>
+  </si>
+  <si>
+    <t>Inter City Courier</t>
+  </si>
+  <si>
+    <t>description_intra_city_courier</t>
+  </si>
+  <si>
+    <t>Intra City Courier</t>
+  </si>
+  <si>
+    <t>description_item_qd</t>
+  </si>
+  <si>
+    <t>{{_UNIT_VALUE}} Item</t>
+  </si>
+  <si>
+    <t>description_items_qd</t>
+  </si>
+  <si>
+    <t>{{_UNIT_VALUE}} Items</t>
+  </si>
+  <si>
+    <t>description_kilogram</t>
+  </si>
+  <si>
+    <t>Kilogram</t>
+  </si>
+  <si>
+    <t>description_life_time_plan</t>
+  </si>
+  <si>
+    <t>Life Time Plan</t>
+  </si>
+  <si>
+    <t>description_location_permission_always_not_granted</t>
+  </si>
+  <si>
+    <t>We need access to your location at all times so passengers can book rides with you, track trips, and ensure you receive requests even if the app is running in the background.</t>
+  </si>
+  <si>
+    <t>description_mercado_pago</t>
+  </si>
+  <si>
+    <t>Mercado Pago</t>
+  </si>
+  <si>
+    <t>description_merchant_mismatch_alert_message_sd</t>
+  </si>
+  <si>
+    <t>You are about to add an item from a different merchant to your cart. This will remove the items from your current cart. Do you want to continue?</t>
+  </si>
+  <si>
+    <t>description_merchant_mismatch_alert_message_ss</t>
+  </si>
+  <si>
+    <t>You are about to add an item from a different category to your cart. This will remove the items from your current cart. Do you want to continue?</t>
+  </si>
+  <si>
+    <t>description_min</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>description_monday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>description_monthly</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>description_movers_and_packers</t>
+  </si>
+  <si>
+    <t>Movers</t>
+  </si>
+  <si>
+    <t>description_mpesa</t>
+  </si>
+  <si>
+    <t>Mpesa</t>
+  </si>
+  <si>
+    <t>description_multiple_service_alert_message_ss</t>
+  </si>
+  <si>
+    <t>The category does not allow multiple services at a time</t>
+  </si>
+  <si>
+    <t>description_name_courier</t>
+  </si>
+  <si>
+    <t>Name: {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_navigation_map</t>
+  </si>
+  <si>
+    <t>Navigation map</t>
+  </si>
+  <si>
+    <t>description_navigation_map_setting_toggle</t>
+  </si>
+  <si>
+    <t>Select your preferred navigation map</t>
+  </si>
+  <si>
+    <t>description_nestpay</t>
+  </si>
+  <si>
+    <t>NestPay</t>
+  </si>
+  <si>
+    <t>description_on_site_service_tag_ss</t>
+  </si>
+  <si>
+    <t>description_online_service_ss</t>
+  </si>
+  <si>
+    <t>Online Service</t>
+  </si>
+  <si>
+    <t>description_online_service_tag_ss</t>
+  </si>
+  <si>
+    <t>description_only_online_service_ss</t>
+  </si>
+  <si>
+    <t>This location offers only online services</t>
+  </si>
+  <si>
+    <t>description_only_onsite_service_ss</t>
+  </si>
+  <si>
+    <t>This location offers only on-site service</t>
+  </si>
+  <si>
+    <t>description_only_pickup_service_ss</t>
+  </si>
+  <si>
+    <t>This location only offers service at home</t>
+  </si>
+  <si>
+    <t>description_order_pick_date</t>
+  </si>
+  <si>
+    <t>Order Pickup Time: {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_ordered_for</t>
+  </si>
+  <si>
+    <t>Ordered For</t>
+  </si>
+  <si>
+    <t>description_pago</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>description_paymob</t>
+  </si>
+  <si>
+    <t>Paymob</t>
+  </si>
+  <si>
+    <t>description_payu</t>
+  </si>
+  <si>
+    <t>PayU</t>
+  </si>
+  <si>
+    <t>description_pending</t>
+  </si>
+  <si>
+    <t>description_phone_courier</t>
+  </si>
+  <si>
+    <t>Phone: {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_pickup_from_qd</t>
+  </si>
+  <si>
+    <t>Pickup from:</t>
+  </si>
+  <si>
+    <t>description_pickup_items</t>
+  </si>
+  <si>
+    <t>Pickup items</t>
+  </si>
+  <si>
+    <t>description_pickup_onsite_tag_ss</t>
+  </si>
+  <si>
+    <t>description_qicard</t>
+  </si>
+  <si>
+    <t>QiCard</t>
+  </si>
+  <si>
+    <t>description_quick_delivery</t>
+  </si>
+  <si>
+    <t>Quick Delivery</t>
+  </si>
+  <si>
+    <t>description_referral_list</t>
+  </si>
+  <si>
+    <t>Referral List</t>
+  </si>
+  <si>
+    <t>description_rejected</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>description_remaining_fuel</t>
+  </si>
+  <si>
+    <t>Remaining Fuel - {{_VALUE}} / {{_VALUE1}} Liter</t>
+  </si>
+  <si>
+    <t>description_repeat_last_customization_sd</t>
+  </si>
+  <si>
+    <t>Repeat last customization?</t>
+  </si>
+  <si>
+    <t>description_return_time</t>
+  </si>
+  <si>
+    <t>Return Time: {{_UNIT_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_saturday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>description_scheduled_time</t>
+  </si>
+  <si>
+    <t>Scheduled Delivery: {{_SCHEDULED_TIME}}</t>
+  </si>
+  <si>
+    <t>description_select_any_one_sd</t>
+  </si>
+  <si>
+    <t>Select any 1</t>
+  </si>
+  <si>
+    <t>description_select_end_time</t>
+  </si>
+  <si>
+    <t>Select end time</t>
+  </si>
+  <si>
+    <t>description_select_minimum_and_upto_sd</t>
+  </si>
+  <si>
+    <t>Select minimun {{_VALUE}} and up to {{_VALUE1}}</t>
+  </si>
+  <si>
+    <t>description_select_start_time</t>
+  </si>
+  <si>
+    <t>Select start time</t>
+  </si>
+  <si>
+    <t>description_select_unit_qd</t>
+  </si>
+  <si>
+    <t>Select Unit</t>
+  </si>
+  <si>
+    <t>description_select_up_to_sd</t>
+  </si>
+  <si>
+    <t>Select up to {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_service</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>description_service_address_ss</t>
+  </si>
+  <si>
+    <t>Service Address</t>
+  </si>
+  <si>
+    <t>description_service_id</t>
+  </si>
+  <si>
+    <t>Service ID {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_standard_delivery</t>
+  </si>
+  <si>
+    <t>Standard Delivery</t>
+  </si>
+  <si>
+    <t>description_status_alert_dropped_courier</t>
+  </si>
+  <si>
+    <t>Are you sure you want to drop this parcels?</t>
+  </si>
+  <si>
+    <t>description_status_alert_picked</t>
+  </si>
+  <si>
+    <t>Are you sure do you want to pick this order?</t>
+  </si>
+  <si>
+    <t>description_status_alert_picked_courier</t>
+  </si>
+  <si>
+    <t>Are you sure you want to pickup this parcels?</t>
+  </si>
+  <si>
+    <t>description_status_arrived_near_destination_qd</t>
+  </si>
+  <si>
+    <t>The delivery partner has arrived near your location.</t>
+  </si>
+  <si>
+    <t>description_status_merchant_accepted_qd</t>
+  </si>
+  <si>
+    <t>The merchant is accepted your order.</t>
+  </si>
+  <si>
+    <t>description_status_merchant_preparing_qd</t>
+  </si>
+  <si>
+    <t>The merchant is preparing your order.</t>
+  </si>
+  <si>
+    <t>description_status_order_is_ready</t>
+  </si>
+  <si>
+    <t>Order is ready for pickup.</t>
+  </si>
+  <si>
+    <t>description_status_picked_qd</t>
+  </si>
+  <si>
+    <t>The Order is picked by our delivery partner.</t>
+  </si>
+  <si>
+    <t>description_status_requested_qd</t>
+  </si>
+  <si>
+    <t>Waiting for the merchant to accept your order.</t>
+  </si>
+  <si>
+    <t>description_status_started_qd</t>
+  </si>
+  <si>
+    <t>The delivery partner is on the way to your location.</t>
+  </si>
+  <si>
+    <t>description_subscription</t>
+  </si>
+  <si>
+    <t>description_sunday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>description_support_ticket_status_closed</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>description_support_ticket_status_open</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>description_support_ticket_status_reopen</t>
+  </si>
+  <si>
+    <t>REOPEN</t>
+  </si>
+  <si>
+    <t>description_sure_call_sos</t>
+  </si>
+  <si>
+    <t>Are you sure want to call SOS?</t>
+  </si>
+  <si>
+    <t>description_thursday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>description_tuesday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>description_upload_images</t>
+  </si>
+  <si>
+    <t>Upload Images</t>
+  </si>
+  <si>
+    <t>description_upload_parcel</t>
+  </si>
+  <si>
+    <t>Upload parcel images from camera</t>
+  </si>
+  <si>
+    <t>description_uploaded</t>
+  </si>
+  <si>
+    <t>Uploaded</t>
+  </si>
+  <si>
+    <t>description_user_approval_edit_item</t>
+  </si>
+  <si>
+    <t>User approval is pending for edit item</t>
+  </si>
+  <si>
+    <t>description_value_of_parcel</t>
+  </si>
+  <si>
+    <t>Value of parcel - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_vehicle_delete_alert_title</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete your vehicle?</t>
+  </si>
+  <si>
+    <t>description_wednesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>description_weekly</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>description_weight</t>
+  </si>
+  <si>
+    <t>Weight - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_will_pickup_sec_qd</t>
+  </si>
+  <si>
+    <t>Will be packed in {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_your_plan_expires_in_days</t>
+  </si>
+  <si>
+    <t>Your plan expires in {{_VALUE}} days!</t>
+  </si>
+  <si>
+    <t>description_zaincash</t>
+  </si>
+  <si>
+    <t>ZainCash</t>
+  </si>
+  <si>
+    <t>error_discount_amount_should_not_greater_than_price</t>
+  </si>
+  <si>
+    <t>Discount amount should not be greater than price</t>
+  </si>
+  <si>
+    <t>error_enter_valid_redeem_point</t>
+  </si>
+  <si>
+    <t>error_no_service_found_ss</t>
+  </si>
+  <si>
+    <t>No Service Found</t>
+  </si>
+  <si>
+    <t>error_only_units_allowed_for_product_sd</t>
+  </si>
+  <si>
+    <t>Only {{_VALUE}} units are allowed for this product</t>
+  </si>
+  <si>
+    <t>error_phone_not_valid</t>
+  </si>
+  <si>
+    <t>Phone number not valid</t>
+  </si>
+  <si>
+    <t>error_phone_number_cannot_be_the_same</t>
+  </si>
+  <si>
+    <t>Phone number cannot be the same as your default phone number.</t>
+  </si>
+  <si>
+    <t>error_please_add_location</t>
+  </si>
+  <si>
+    <t>Please Add Location</t>
+  </si>
+  <si>
+    <t>error_please_complete_all_services</t>
+  </si>
+  <si>
+    <t>Please complete all services</t>
+  </si>
+  <si>
+    <t>error_please_enter_cancel_reason</t>
+  </si>
+  <si>
+    <t>Please enter cancellation reason</t>
+  </si>
+  <si>
+    <t>error_please_enter_device_identifier</t>
+  </si>
+  <si>
+    <t>Please enter valid 11-digit device identifier</t>
+  </si>
+  <si>
+    <t>error_please_enter_discount_price_ss</t>
+  </si>
+  <si>
+    <t>Please enter discount price</t>
+  </si>
+  <si>
+    <t>error_please_enter_emergency_contact_name</t>
+  </si>
+  <si>
+    <t>Please enter emergency contact name</t>
+  </si>
+  <si>
+    <t>error_please_enter_making_of_payment_device</t>
+  </si>
+  <si>
+    <t>Please enter making of payment device</t>
+  </si>
+  <si>
+    <t>error_please_enter_personal_id_number</t>
+  </si>
+  <si>
+    <t>Please enter valid 11-digit personal identification number</t>
+  </si>
+  <si>
+    <t>error_please_enter_price_ss</t>
+  </si>
+  <si>
+    <t>Please enter price</t>
+  </si>
+  <si>
+    <t>error_please_scan_all_parcel</t>
+  </si>
+  <si>
+    <t>Please scan all parcels</t>
+  </si>
+  <si>
+    <t>error_please_select_day_first</t>
+  </si>
+  <si>
+    <t>Please select day first</t>
+  </si>
+  <si>
+    <t>error_please_select_end_time</t>
+  </si>
+  <si>
+    <t>Please select end time</t>
+  </si>
+  <si>
+    <t>error_please_select_modifier_value_sd</t>
+  </si>
+  <si>
+    <t>Please select {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>error_please_select_service</t>
+  </si>
+  <si>
+    <t>Please select Services</t>
+  </si>
+  <si>
+    <t>error_please_select_start_time</t>
+  </si>
+  <si>
+    <t>Please select start time</t>
+  </si>
+  <si>
+    <t>error_please_select_valid_end_time</t>
+  </si>
+  <si>
+    <t>Please select valid end time</t>
+  </si>
+  <si>
+    <t>error_please_select_valid_timeslot</t>
+  </si>
+  <si>
+    <t>Please select valid timeslot</t>
+  </si>
+  <si>
+    <t>error_please_upload_parcel_image</t>
+  </si>
+  <si>
+    <t>Please upload parcel image</t>
+  </si>
+  <si>
+    <t>error_service_cart_empty</t>
+  </si>
+  <si>
+    <t>Please add at least one service to your cart before proceeding.</t>
+  </si>
+  <si>
+    <t>error_store_not_provide_delivery_location_sd</t>
+  </si>
+  <si>
+    <t>The store does not provide delivery at your location</t>
+  </si>
+  <si>
+    <t>error_timeslot_already_added</t>
+  </si>
+  <si>
+    <t>Timeslot already added</t>
+  </si>
+  <si>
+    <t>error_you_can_only_select_up_to_options_sd</t>
+  </si>
+  <si>
+    <t>You can only select up to {{_VALUE}} options</t>
+  </si>
+  <si>
+    <t>heading_accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>heading_add_slots</t>
+  </si>
+  <si>
+    <t>Add Slots</t>
+  </si>
+  <si>
+    <t>heading_availability</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>heading_bank</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>heading_booking_cancelled</t>
+  </si>
+  <si>
+    <t>Booking Cancelled</t>
+  </si>
+  <si>
+    <t>heading_cart_qd</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>heading_change_merchant_sd</t>
+  </si>
+  <si>
+    <t>Change Merchant?</t>
+  </si>
+  <si>
+    <t>heading_change_merchant_ss</t>
+  </si>
+  <si>
+    <t>Change Category?</t>
+  </si>
+  <si>
+    <t>heading_change_service_ss</t>
+  </si>
+  <si>
+    <t>Change Service?</t>
+  </si>
+  <si>
+    <t>heading_delete_address</t>
+  </si>
+  <si>
+    <t>Delete Address</t>
+  </si>
+  <si>
+    <t>heading_fix_group_booking</t>
+  </si>
+  <si>
+    <t>Fix Group Bookings</t>
+  </si>
+  <si>
+    <t>heading_manage_service</t>
+  </si>
+  <si>
+    <t>Manage Service</t>
+  </si>
+  <si>
+    <t>heading_message_to_your_driver</t>
+  </si>
+  <si>
+    <t>Message to your driver</t>
+  </si>
+  <si>
+    <t>heading_select_services</t>
+  </si>
+  <si>
+    <t>Select Service</t>
+  </si>
+  <si>
+    <t>heading_set_time</t>
+  </si>
+  <si>
+    <t>Set Time</t>
+  </si>
+  <si>
+    <t>hint_device_identifier</t>
+  </si>
+  <si>
+    <t>Device Identifier</t>
+  </si>
+  <si>
+    <t>hint_discount_price</t>
+  </si>
+  <si>
+    <t>Discount Price</t>
+  </si>
+  <si>
+    <t>hint_making_of_payment_device</t>
+  </si>
+  <si>
+    <t>Making Of Payment Device</t>
+  </si>
+  <si>
+    <t>hint_personal_identification_number</t>
+  </si>
+  <si>
+    <t>Personal Identification Number</t>
+  </si>
+  <si>
+    <t>hint_price</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>hint_search_from_phone_contact</t>
+  </si>
+  <si>
+    <t>Search from phone contacts</t>
+  </si>
+  <si>
+    <t>hint_write_notes</t>
+  </si>
+  <si>
+    <t>Write notes</t>
+  </si>
+  <si>
+    <t>sub_heading_delivery_details</t>
+  </si>
+  <si>
+    <t>Delivery Details</t>
+  </si>
+  <si>
+    <t>sub_heading_discount_price</t>
+  </si>
+  <si>
+    <t>sub_heading_fallback_vehicles</t>
+  </si>
+  <si>
+    <t>FallBack Vehicles</t>
+  </si>
+  <si>
+    <t>sub_heading_full_day_available</t>
+  </si>
+  <si>
+    <t>Full Day Available</t>
+  </si>
+  <si>
+    <t>sub_heading_price</t>
+  </si>
+  <si>
+    <t>sub_heading_service_details_ss</t>
+  </si>
+  <si>
+    <t>Service Details</t>
+  </si>
+  <si>
+    <t>sub_heading_slots</t>
+  </si>
+  <si>
+    <t>Slots</t>
   </si>
 </sst>
 </file>
@@ -2027,7 +3245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I276"/>
+  <dimension ref="A1:I486"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="10" customWidth="1"/>
@@ -5125,6 +6343,2316 @@
         <v>544</v>
       </c>
     </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>545</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="C277" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>547</v>
+      </c>
+      <c r="B278" t="s">
+        <v>10</v>
+      </c>
+      <c r="C278" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>549</v>
+      </c>
+      <c r="B279" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>551</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>553</v>
+      </c>
+      <c r="B281" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>555</v>
+      </c>
+      <c r="B282" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>557</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>559</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>561</v>
+      </c>
+      <c r="B285" t="s">
+        <v>10</v>
+      </c>
+      <c r="C285" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>563</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>565</v>
+      </c>
+      <c r="B287" t="s">
+        <v>10</v>
+      </c>
+      <c r="C287" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>567</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>569</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>571</v>
+      </c>
+      <c r="B290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>573</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="C291" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>575</v>
+      </c>
+      <c r="B292" t="s">
+        <v>10</v>
+      </c>
+      <c r="C292" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>577</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>579</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>581</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>582</v>
+      </c>
+      <c r="B296" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>584</v>
+      </c>
+      <c r="B297" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>585</v>
+      </c>
+      <c r="B298" t="s">
+        <v>10</v>
+      </c>
+      <c r="C298" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>587</v>
+      </c>
+      <c r="B299" t="s">
+        <v>10</v>
+      </c>
+      <c r="C299" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>588</v>
+      </c>
+      <c r="B300" t="s">
+        <v>10</v>
+      </c>
+      <c r="C300" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>590</v>
+      </c>
+      <c r="B301" t="s">
+        <v>10</v>
+      </c>
+      <c r="C301" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>591</v>
+      </c>
+      <c r="B302" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>593</v>
+      </c>
+      <c r="B303" t="s">
+        <v>10</v>
+      </c>
+      <c r="C303" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>595</v>
+      </c>
+      <c r="B304" t="s">
+        <v>10</v>
+      </c>
+      <c r="C304" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>597</v>
+      </c>
+      <c r="B305" t="s">
+        <v>10</v>
+      </c>
+      <c r="C305" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>599</v>
+      </c>
+      <c r="B306" t="s">
+        <v>10</v>
+      </c>
+      <c r="C306" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>601</v>
+      </c>
+      <c r="B307" t="s">
+        <v>10</v>
+      </c>
+      <c r="C307" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>603</v>
+      </c>
+      <c r="B308" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>605</v>
+      </c>
+      <c r="B309" t="s">
+        <v>10</v>
+      </c>
+      <c r="C309" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>607</v>
+      </c>
+      <c r="B310" t="s">
+        <v>10</v>
+      </c>
+      <c r="C310" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>609</v>
+      </c>
+      <c r="B311" t="s">
+        <v>10</v>
+      </c>
+      <c r="C311" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>611</v>
+      </c>
+      <c r="B312" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>613</v>
+      </c>
+      <c r="B313" t="s">
+        <v>10</v>
+      </c>
+      <c r="C313" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>615</v>
+      </c>
+      <c r="B314" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>617</v>
+      </c>
+      <c r="B315" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>619</v>
+      </c>
+      <c r="B316" t="s">
+        <v>10</v>
+      </c>
+      <c r="C316" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>620</v>
+      </c>
+      <c r="B317" t="s">
+        <v>10</v>
+      </c>
+      <c r="C317" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>622</v>
+      </c>
+      <c r="B318" t="s">
+        <v>10</v>
+      </c>
+      <c r="C318" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>624</v>
+      </c>
+      <c r="B319" t="s">
+        <v>10</v>
+      </c>
+      <c r="C319" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>626</v>
+      </c>
+      <c r="B320" t="s">
+        <v>10</v>
+      </c>
+      <c r="C320" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>628</v>
+      </c>
+      <c r="B321" t="s">
+        <v>10</v>
+      </c>
+      <c r="C321" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>629</v>
+      </c>
+      <c r="B322" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>631</v>
+      </c>
+      <c r="B323" t="s">
+        <v>10</v>
+      </c>
+      <c r="C323" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>633</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>635</v>
+      </c>
+      <c r="B325" t="s">
+        <v>10</v>
+      </c>
+      <c r="C325" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>637</v>
+      </c>
+      <c r="B326" t="s">
+        <v>10</v>
+      </c>
+      <c r="C326" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>639</v>
+      </c>
+      <c r="B327" t="s">
+        <v>10</v>
+      </c>
+      <c r="C327" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>641</v>
+      </c>
+      <c r="B328" t="s">
+        <v>10</v>
+      </c>
+      <c r="C328" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>643</v>
+      </c>
+      <c r="B329" t="s">
+        <v>10</v>
+      </c>
+      <c r="C329" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>645</v>
+      </c>
+      <c r="B330" t="s">
+        <v>10</v>
+      </c>
+      <c r="C330" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>647</v>
+      </c>
+      <c r="B331" t="s">
+        <v>10</v>
+      </c>
+      <c r="C331" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>649</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>651</v>
+      </c>
+      <c r="B333" t="s">
+        <v>10</v>
+      </c>
+      <c r="C333" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>653</v>
+      </c>
+      <c r="B334" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>655</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>657</v>
+      </c>
+      <c r="B336" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>659</v>
+      </c>
+      <c r="B337" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>661</v>
+      </c>
+      <c r="B338" t="s">
+        <v>10</v>
+      </c>
+      <c r="C338" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>663</v>
+      </c>
+      <c r="B339" t="s">
+        <v>10</v>
+      </c>
+      <c r="C339" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>665</v>
+      </c>
+      <c r="B340" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>667</v>
+      </c>
+      <c r="B341" t="s">
+        <v>10</v>
+      </c>
+      <c r="C341" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>669</v>
+      </c>
+      <c r="B342" t="s">
+        <v>10</v>
+      </c>
+      <c r="C342" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>671</v>
+      </c>
+      <c r="B343" t="s">
+        <v>10</v>
+      </c>
+      <c r="C343" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>673</v>
+      </c>
+      <c r="B344" t="s">
+        <v>10</v>
+      </c>
+      <c r="C344" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>675</v>
+      </c>
+      <c r="B345" t="s">
+        <v>10</v>
+      </c>
+      <c r="C345" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>677</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+      <c r="C346" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>679</v>
+      </c>
+      <c r="B347" t="s">
+        <v>10</v>
+      </c>
+      <c r="C347" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>681</v>
+      </c>
+      <c r="B348" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>683</v>
+      </c>
+      <c r="B349" t="s">
+        <v>10</v>
+      </c>
+      <c r="C349" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>685</v>
+      </c>
+      <c r="B350" t="s">
+        <v>10</v>
+      </c>
+      <c r="C350" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>687</v>
+      </c>
+      <c r="B351" t="s">
+        <v>10</v>
+      </c>
+      <c r="C351" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>689</v>
+      </c>
+      <c r="B352" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>691</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>693</v>
+      </c>
+      <c r="B354" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>695</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>697</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>699</v>
+      </c>
+      <c r="B357" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>701</v>
+      </c>
+      <c r="B358" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>703</v>
+      </c>
+      <c r="B359" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>705</v>
+      </c>
+      <c r="B360" t="s">
+        <v>10</v>
+      </c>
+      <c r="C360" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>707</v>
+      </c>
+      <c r="B361" t="s">
+        <v>10</v>
+      </c>
+      <c r="C361" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>709</v>
+      </c>
+      <c r="B362" t="s">
+        <v>10</v>
+      </c>
+      <c r="C362" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>711</v>
+      </c>
+      <c r="B363" t="s">
+        <v>10</v>
+      </c>
+      <c r="C363" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>713</v>
+      </c>
+      <c r="B364" t="s">
+        <v>10</v>
+      </c>
+      <c r="C364" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>715</v>
+      </c>
+      <c r="B365" t="s">
+        <v>10</v>
+      </c>
+      <c r="C365" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>716</v>
+      </c>
+      <c r="B366" t="s">
+        <v>10</v>
+      </c>
+      <c r="C366" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>718</v>
+      </c>
+      <c r="B367" t="s">
+        <v>10</v>
+      </c>
+      <c r="C367" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>719</v>
+      </c>
+      <c r="B368" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>721</v>
+      </c>
+      <c r="B369" t="s">
+        <v>10</v>
+      </c>
+      <c r="C369" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>723</v>
+      </c>
+      <c r="B370" t="s">
+        <v>10</v>
+      </c>
+      <c r="C370" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>725</v>
+      </c>
+      <c r="B371" t="s">
+        <v>10</v>
+      </c>
+      <c r="C371" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>727</v>
+      </c>
+      <c r="B372" t="s">
+        <v>10</v>
+      </c>
+      <c r="C372" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>729</v>
+      </c>
+      <c r="B373" t="s">
+        <v>10</v>
+      </c>
+      <c r="C373" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>731</v>
+      </c>
+      <c r="B374" t="s">
+        <v>10</v>
+      </c>
+      <c r="C374" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>733</v>
+      </c>
+      <c r="B375" t="s">
+        <v>10</v>
+      </c>
+      <c r="C375" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>735</v>
+      </c>
+      <c r="B376" t="s">
+        <v>10</v>
+      </c>
+      <c r="C376" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>736</v>
+      </c>
+      <c r="B377" t="s">
+        <v>10</v>
+      </c>
+      <c r="C377" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>738</v>
+      </c>
+      <c r="B378" t="s">
+        <v>10</v>
+      </c>
+      <c r="C378" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>740</v>
+      </c>
+      <c r="B379" t="s">
+        <v>10</v>
+      </c>
+      <c r="C379" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>742</v>
+      </c>
+      <c r="B380" t="s">
+        <v>10</v>
+      </c>
+      <c r="C380" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>743</v>
+      </c>
+      <c r="B381" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>745</v>
+      </c>
+      <c r="B382" t="s">
+        <v>10</v>
+      </c>
+      <c r="C382" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>747</v>
+      </c>
+      <c r="B383" t="s">
+        <v>10</v>
+      </c>
+      <c r="C383" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>749</v>
+      </c>
+      <c r="B384" t="s">
+        <v>10</v>
+      </c>
+      <c r="C384" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>751</v>
+      </c>
+      <c r="B385" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>753</v>
+      </c>
+      <c r="B386" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>755</v>
+      </c>
+      <c r="B387" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>757</v>
+      </c>
+      <c r="B388" t="s">
+        <v>10</v>
+      </c>
+      <c r="C388" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>759</v>
+      </c>
+      <c r="B389" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>761</v>
+      </c>
+      <c r="B390" t="s">
+        <v>10</v>
+      </c>
+      <c r="C390" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>763</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>765</v>
+      </c>
+      <c r="B392" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>767</v>
+      </c>
+      <c r="B393" t="s">
+        <v>10</v>
+      </c>
+      <c r="C393" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>769</v>
+      </c>
+      <c r="B394" t="s">
+        <v>10</v>
+      </c>
+      <c r="C394" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>771</v>
+      </c>
+      <c r="B395" t="s">
+        <v>10</v>
+      </c>
+      <c r="C395" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>773</v>
+      </c>
+      <c r="B396" t="s">
+        <v>10</v>
+      </c>
+      <c r="C396" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>775</v>
+      </c>
+      <c r="B397" t="s">
+        <v>10</v>
+      </c>
+      <c r="C397" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>777</v>
+      </c>
+      <c r="B398" t="s">
+        <v>10</v>
+      </c>
+      <c r="C398" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>779</v>
+      </c>
+      <c r="B399" t="s">
+        <v>10</v>
+      </c>
+      <c r="C399" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>781</v>
+      </c>
+      <c r="B400" t="s">
+        <v>10</v>
+      </c>
+      <c r="C400" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>783</v>
+      </c>
+      <c r="B401" t="s">
+        <v>10</v>
+      </c>
+      <c r="C401" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>785</v>
+      </c>
+      <c r="B402" t="s">
+        <v>10</v>
+      </c>
+      <c r="C402" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>787</v>
+      </c>
+      <c r="B403" t="s">
+        <v>10</v>
+      </c>
+      <c r="C403" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>789</v>
+      </c>
+      <c r="B404" t="s">
+        <v>10</v>
+      </c>
+      <c r="C404" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>791</v>
+      </c>
+      <c r="B405" t="s">
+        <v>10</v>
+      </c>
+      <c r="C405" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>793</v>
+      </c>
+      <c r="B406" t="s">
+        <v>10</v>
+      </c>
+      <c r="C406" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>795</v>
+      </c>
+      <c r="B407" t="s">
+        <v>10</v>
+      </c>
+      <c r="C407" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>797</v>
+      </c>
+      <c r="B408" t="s">
+        <v>10</v>
+      </c>
+      <c r="C408" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>799</v>
+      </c>
+      <c r="B409" t="s">
+        <v>10</v>
+      </c>
+      <c r="C409" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>801</v>
+      </c>
+      <c r="B410" t="s">
+        <v>10</v>
+      </c>
+      <c r="C410" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>802</v>
+      </c>
+      <c r="B411" t="s">
+        <v>10</v>
+      </c>
+      <c r="C411" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>804</v>
+      </c>
+      <c r="B412" t="s">
+        <v>10</v>
+      </c>
+      <c r="C412" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>806</v>
+      </c>
+      <c r="B413" t="s">
+        <v>10</v>
+      </c>
+      <c r="C413" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>808</v>
+      </c>
+      <c r="B414" t="s">
+        <v>10</v>
+      </c>
+      <c r="C414" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>810</v>
+      </c>
+      <c r="B415" t="s">
+        <v>10</v>
+      </c>
+      <c r="C415" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>812</v>
+      </c>
+      <c r="B416" t="s">
+        <v>10</v>
+      </c>
+      <c r="C416" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>814</v>
+      </c>
+      <c r="B417" t="s">
+        <v>10</v>
+      </c>
+      <c r="C417" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>816</v>
+      </c>
+      <c r="B418" t="s">
+        <v>10</v>
+      </c>
+      <c r="C418" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>818</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>820</v>
+      </c>
+      <c r="B420" t="s">
+        <v>10</v>
+      </c>
+      <c r="C420" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>822</v>
+      </c>
+      <c r="B421" t="s">
+        <v>10</v>
+      </c>
+      <c r="C421" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>824</v>
+      </c>
+      <c r="B422" t="s">
+        <v>10</v>
+      </c>
+      <c r="C422" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>826</v>
+      </c>
+      <c r="B423" t="s">
+        <v>10</v>
+      </c>
+      <c r="C423" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>828</v>
+      </c>
+      <c r="B424" t="s">
+        <v>10</v>
+      </c>
+      <c r="C424" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>830</v>
+      </c>
+      <c r="B425" t="s">
+        <v>10</v>
+      </c>
+      <c r="C425" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>832</v>
+      </c>
+      <c r="B426" t="s">
+        <v>10</v>
+      </c>
+      <c r="C426" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>834</v>
+      </c>
+      <c r="B427" t="s">
+        <v>10</v>
+      </c>
+      <c r="C427" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>836</v>
+      </c>
+      <c r="B428" t="s">
+        <v>10</v>
+      </c>
+      <c r="C428" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>838</v>
+      </c>
+      <c r="B429" t="s">
+        <v>10</v>
+      </c>
+      <c r="C429" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>840</v>
+      </c>
+      <c r="B430" t="s">
+        <v>10</v>
+      </c>
+      <c r="C430" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>842</v>
+      </c>
+      <c r="B431" t="s">
+        <v>10</v>
+      </c>
+      <c r="C431" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>843</v>
+      </c>
+      <c r="B432" t="s">
+        <v>10</v>
+      </c>
+      <c r="C432" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>845</v>
+      </c>
+      <c r="B433" t="s">
+        <v>10</v>
+      </c>
+      <c r="C433" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>847</v>
+      </c>
+      <c r="B434" t="s">
+        <v>10</v>
+      </c>
+      <c r="C434" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>849</v>
+      </c>
+      <c r="B435" t="s">
+        <v>10</v>
+      </c>
+      <c r="C435" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>851</v>
+      </c>
+      <c r="B436" t="s">
+        <v>10</v>
+      </c>
+      <c r="C436" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>853</v>
+      </c>
+      <c r="B437" t="s">
+        <v>10</v>
+      </c>
+      <c r="C437" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>855</v>
+      </c>
+      <c r="B438" t="s">
+        <v>10</v>
+      </c>
+      <c r="C438" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>857</v>
+      </c>
+      <c r="B439" t="s">
+        <v>10</v>
+      </c>
+      <c r="C439" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>859</v>
+      </c>
+      <c r="B440" t="s">
+        <v>10</v>
+      </c>
+      <c r="C440" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>861</v>
+      </c>
+      <c r="B441" t="s">
+        <v>10</v>
+      </c>
+      <c r="C441" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>863</v>
+      </c>
+      <c r="B442" t="s">
+        <v>10</v>
+      </c>
+      <c r="C442" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>865</v>
+      </c>
+      <c r="B443" t="s">
+        <v>10</v>
+      </c>
+      <c r="C443" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>867</v>
+      </c>
+      <c r="B444" t="s">
+        <v>10</v>
+      </c>
+      <c r="C444" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>869</v>
+      </c>
+      <c r="B445" t="s">
+        <v>10</v>
+      </c>
+      <c r="C445" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>871</v>
+      </c>
+      <c r="B446" t="s">
+        <v>10</v>
+      </c>
+      <c r="C446" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>873</v>
+      </c>
+      <c r="B447" t="s">
+        <v>10</v>
+      </c>
+      <c r="C447" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>875</v>
+      </c>
+      <c r="B448" t="s">
+        <v>10</v>
+      </c>
+      <c r="C448" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>877</v>
+      </c>
+      <c r="B449" t="s">
+        <v>10</v>
+      </c>
+      <c r="C449" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>879</v>
+      </c>
+      <c r="B450" t="s">
+        <v>10</v>
+      </c>
+      <c r="C450" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>881</v>
+      </c>
+      <c r="B451" t="s">
+        <v>10</v>
+      </c>
+      <c r="C451" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>883</v>
+      </c>
+      <c r="B452" t="s">
+        <v>10</v>
+      </c>
+      <c r="C452" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>885</v>
+      </c>
+      <c r="B453" t="s">
+        <v>10</v>
+      </c>
+      <c r="C453" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>887</v>
+      </c>
+      <c r="B454" t="s">
+        <v>10</v>
+      </c>
+      <c r="C454" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>889</v>
+      </c>
+      <c r="B455" t="s">
+        <v>10</v>
+      </c>
+      <c r="C455" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>891</v>
+      </c>
+      <c r="B456" t="s">
+        <v>10</v>
+      </c>
+      <c r="C456" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>893</v>
+      </c>
+      <c r="B457" t="s">
+        <v>10</v>
+      </c>
+      <c r="C457" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>895</v>
+      </c>
+      <c r="B458" t="s">
+        <v>10</v>
+      </c>
+      <c r="C458" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>897</v>
+      </c>
+      <c r="B459" t="s">
+        <v>10</v>
+      </c>
+      <c r="C459" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>899</v>
+      </c>
+      <c r="B460" t="s">
+        <v>10</v>
+      </c>
+      <c r="C460" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>901</v>
+      </c>
+      <c r="B461" t="s">
+        <v>10</v>
+      </c>
+      <c r="C461" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>903</v>
+      </c>
+      <c r="B462" t="s">
+        <v>10</v>
+      </c>
+      <c r="C462" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>905</v>
+      </c>
+      <c r="B463" t="s">
+        <v>10</v>
+      </c>
+      <c r="C463" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>907</v>
+      </c>
+      <c r="B464" t="s">
+        <v>10</v>
+      </c>
+      <c r="C464" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>909</v>
+      </c>
+      <c r="B465" t="s">
+        <v>10</v>
+      </c>
+      <c r="C465" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>911</v>
+      </c>
+      <c r="B466" t="s">
+        <v>10</v>
+      </c>
+      <c r="C466" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>913</v>
+      </c>
+      <c r="B467" t="s">
+        <v>10</v>
+      </c>
+      <c r="C467" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>915</v>
+      </c>
+      <c r="B468" t="s">
+        <v>10</v>
+      </c>
+      <c r="C468" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>917</v>
+      </c>
+      <c r="B469" t="s">
+        <v>10</v>
+      </c>
+      <c r="C469" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>919</v>
+      </c>
+      <c r="B470" t="s">
+        <v>10</v>
+      </c>
+      <c r="C470" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>921</v>
+      </c>
+      <c r="B471" t="s">
+        <v>10</v>
+      </c>
+      <c r="C471" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>923</v>
+      </c>
+      <c r="B472" t="s">
+        <v>10</v>
+      </c>
+      <c r="C472" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>925</v>
+      </c>
+      <c r="B473" t="s">
+        <v>10</v>
+      </c>
+      <c r="C473" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>927</v>
+      </c>
+      <c r="B474" t="s">
+        <v>10</v>
+      </c>
+      <c r="C474" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>929</v>
+      </c>
+      <c r="B475" t="s">
+        <v>10</v>
+      </c>
+      <c r="C475" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>931</v>
+      </c>
+      <c r="B476" t="s">
+        <v>10</v>
+      </c>
+      <c r="C476" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>933</v>
+      </c>
+      <c r="B477" t="s">
+        <v>10</v>
+      </c>
+      <c r="C477" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>935</v>
+      </c>
+      <c r="B478" t="s">
+        <v>10</v>
+      </c>
+      <c r="C478" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>937</v>
+      </c>
+      <c r="B479" t="s">
+        <v>10</v>
+      </c>
+      <c r="C479" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>939</v>
+      </c>
+      <c r="B480" t="s">
+        <v>10</v>
+      </c>
+      <c r="C480" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>941</v>
+      </c>
+      <c r="B481" t="s">
+        <v>10</v>
+      </c>
+      <c r="C481" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>942</v>
+      </c>
+      <c r="B482" t="s">
+        <v>10</v>
+      </c>
+      <c r="C482" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>944</v>
+      </c>
+      <c r="B483" t="s">
+        <v>10</v>
+      </c>
+      <c r="C483" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>946</v>
+      </c>
+      <c r="B484" t="s">
+        <v>10</v>
+      </c>
+      <c r="C484" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>947</v>
+      </c>
+      <c r="B485" t="s">
+        <v>10</v>
+      </c>
+      <c r="C485" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>949</v>
+      </c>
+      <c r="B486" t="s">
+        <v>10</v>
+      </c>
+      <c r="C486" t="s">
+        <v>950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
